--- a/Assets/Resources/DataFiles/ItemData/ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/ExcelFile/ItemDataTable.xlsx
@@ -5,25 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\WJ_TestPlace\Data\Item\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ItemData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32DECDA-3298-4E7D-96E5-549785D54876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE9C24E-727B-40CD-AB63-AA36B455C683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ArmorDefinitions" sheetId="1" r:id="rId1"/>
     <sheet name="WeaponDefinitions" sheetId="7" r:id="rId2"/>
     <sheet name="PotionDefinitions" sheetId="2" r:id="rId3"/>
-    <sheet name="ComboBox" sheetId="9" r:id="rId4"/>
+    <sheet name="RelicDefinitions" sheetId="10" r:id="rId4"/>
+    <sheet name="ComboBox" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
   <si>
     <t>itemId</t>
   </si>
@@ -100,10 +101,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>itemName_kr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -136,10 +133,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>weaponClass</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Fighter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -205,6 +198,17 @@
   </si>
   <si>
     <t>포션입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uniqueEffectId</t>
+  </si>
+  <si>
+    <t>characterClass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weaponType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -555,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.8984375" customWidth="1"/>
@@ -564,30 +568,30 @@
     <col min="6" max="6" width="18.69921875" customWidth="1"/>
     <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="22.5" customWidth="1"/>
-    <col min="10" max="10" width="39.09765625" customWidth="1"/>
-    <col min="11" max="11" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.5" customWidth="1"/>
+    <col min="11" max="11" width="39.09765625" customWidth="1"/>
+    <col min="12" max="12" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G1" t="s">
         <v>8</v>
@@ -599,19 +603,22 @@
         <v>23</v>
       </c>
       <c r="J1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -631,19 +638,19 @@
         <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
         <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
         <v>21</v>
@@ -651,8 +658,11 @@
       <c r="M2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -660,34 +670,34 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>15</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -695,10 +705,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -709,73 +719,73 @@
       <c r="G4">
         <v>30</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>19</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3001</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G5">
         <v>1.2</v>
       </c>
-      <c r="J5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
+      <c r="K5" t="s">
+        <v>39</v>
       </c>
       <c r="L5">
         <v>2</v>
       </c>
       <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -785,7 +795,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98D531FC-6AF7-4606-979D-AC68BC0E3AF4}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.8984375" customWidth="1"/>
@@ -796,23 +806,24 @@
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="15.3984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="39.09765625" customWidth="1"/>
-    <col min="12" max="12" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5" customWidth="1"/>
+    <col min="12" max="12" width="39.09765625" customWidth="1"/>
+    <col min="13" max="13" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -830,22 +841,25 @@
         <v>23</v>
       </c>
       <c r="J1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" t="s">
         <v>1</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -865,13 +879,13 @@
         <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
         <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
@@ -880,7 +894,7 @@
         <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s">
         <v>21</v>
@@ -888,8 +902,11 @@
       <c r="N2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>4001</v>
       </c>
@@ -897,10 +914,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -912,33 +929,33 @@
         <v>45</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
         <v>11</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>2</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>4</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>4501</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -952,38 +969,38 @@
       <c r="J4" t="s">
         <v>20</v>
       </c>
-      <c r="K4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4">
         <v>4</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>2</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>1300</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -993,44 +1010,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.8984375" customWidth="1"/>
     <col min="2" max="3" width="18.296875" customWidth="1"/>
-    <col min="5" max="5" width="39.09765625" customWidth="1"/>
-    <col min="6" max="6" width="10.296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.59765625" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
+    <col min="6" max="6" width="39.09765625" customWidth="1"/>
+    <col min="7" max="7" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1047,7 +1068,7 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
         <v>21</v>
@@ -1055,50 +1076,53 @@
       <c r="H2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>5001</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+      <c r="F3" t="s">
+        <v>48</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1107,6 +1131,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F020980-020C-4DC2-B75B-0B61477EE825}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7307A133-7AC2-4128-A64F-60161F6862FE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>

--- a/Assets/Resources/DataFiles/ItemData/ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/ExcelFile/ItemDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ItemData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE9C24E-727B-40CD-AB63-AA36B455C683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995EDDD7-6323-413D-8802-738D51298CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ArmorDefinitions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="56">
   <si>
     <t>itemId</t>
   </si>
@@ -210,6 +210,21 @@
   <si>
     <t>weaponType</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀀텀 슈즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하이-테크놀로지가 탑재된 신발입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UniqueEffect_QuantumShoes</t>
   </si>
 </sst>
 </file>
@@ -767,6 +782,44 @@
         <v>150</v>
       </c>
     </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>3002</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>1500</v>
+      </c>
+    </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
